--- a/SGC-CKN/Excel/076721bc-1422-4160-a740-b3d01c74c0b0_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P280_D1200_14-04-2026.xlsx
+++ b/SGC-CKN/Excel/076721bc-1422-4160-a740-b3d01c74c0b0_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P280_D1200_14-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P280</t>
+    <t>P260</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
